--- a/test-cases/tcs.xlsx
+++ b/test-cases/tcs.xlsx
@@ -9,6 +9,7 @@
     <sheet name="mystc5 OnePool Automation Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mystc5 Add to cart Automation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Pre-Order Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Test Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -71,7 +72,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +165,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8759,4 +8768,826 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Real value in APP</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Description / required state</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Used in TC IDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>PUBLIC_USER</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Public user (not logged in)</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Continue as public user; no login</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>OP4</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-001, COMINGSOON-UI-005, COMINGSOON-UI-006, COMINGSOON-UI-007, COMINGSOON-UI-008, COMINGSOON-UI-009, COMINGSOON-UI-010, COMINGSOON-UI-011, COMINGSOON-UI-012, COMINGSOON-UI-014, COMINGSOON-UI-018, COMINGSOON-UI-022, COMINGSOON-UI-023, COMINGSOON-UI-029, COMINGSOON-UI-031, PREORDER-UI-001, PREORDER-UI-007, PREORDER-UI-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>LOGIN_USER_PRIMARY</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>504563459</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Full login (private user)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>OP1</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>41, 42, COMINGSOON-UI-002, COMINGSOON-UI-005, COMINGSOON-UI-007, COMINGSOON-UI-009, COMINGSOON-UI-010, COMINGSOON-UI-012, COMINGSOON-UI-013, COMINGSOON-UI-014, COMINGSOON-UI-015, COMINGSOON-UI-016, COMINGSOON-UI-017, COMINGSOON-UI-018, COMINGSOON-UI-019, COMINGSOON-UI-023, COMINGSOON-UI-024, COMINGSOON-UI-026, COMINGSOON-UI-027, COMINGSOON-UI-028, COMINGSOON-UI-030, COMINGSOON-UI-031, COMINGSOON-UI-032, COMINGSOON-UI-033, PREORDER-UI-001, PREORDER-UI-002, PREORDER-UI-003, PREORDER-UI-004, PREORDER-UI-008, PREORDER-UI-012, PREORDER-UI-013, PREORDER-UI-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>OTP_USER_PRIMARY</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>504563459</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>OTP login with primary number</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>OP7</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-003, COMINGSOON-UI-020, COMINGSOON-UI-025, PREORDER-UI-005, PREORDER-UI-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>OTP_USER_SECONDARY</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>0507127863</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>OTP login with secondary number - limited access</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>OP8 / OP13</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-004, COMINGSOON-UI-006, COMINGSOON-UI-009, COMINGSOON-UI-010, COMINGSOON-UI-011, COMINGSOON-UI-021, COMINGSOON-UI-030, PREORDER-UI-001, PREORDER-UI-006, PREORDER-UI-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>DEV_NORMAL_INSTOCK</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>WHOOP PEAK BAND 5.0</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Normal in-stock device, Wearables category</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>User (Add to cart #36)</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-005, PREORDER-UI-012, PREORDER-UI-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>DEV_PARTIAL_OOS</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PLUS 6TH</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Smart phones; Variation A out of stock, Variation B in stock</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>DEV_FREE_DEVICE</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PLUS 6TH</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Smart phones; supports Free Device option</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ELIGIBLE_VOICE_POSTPAID</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>504563459</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Line with active offer, used for Free Device</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_TIMER</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y, releaseDate = now + 2d 03h 00m, price set</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 / MS-4095</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-010, COMINGSOON-UI-011, COMINGSOON-UI-015, COMINGSOON-UI-017, COMINGSOON-UI-018, COMINGSOON-UI-019, COMINGSOON-UI-020, COMINGSOON-UI-021, COMINGSOON-UI-022, COMINGSOON-UI-024, COMINGSOON-UI-025, COMINGSOON-UI-026, COMINGSOON-UI-027, COMINGSOON-UI-028, COMINGSOON-UI-032</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_NODATE</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y, releaseDate empty/null, price set</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P4</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-009, COMINGSOON-UI-018, COMINGSOON-UI-019, COMINGSOON-UI-020, COMINGSOON-UI-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_LT1DAY</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y; releaseDate = now + 5h / + 120d / + 2 min (DEV_CS_SHORT purchasable after release)</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>MS-4095</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_FAR</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y; releaseDate = now + 5h / + 120d / + 2 min (DEV_CS_SHORT purchasable after release)</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>MS-4095</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_SHORT</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y; releaseDate = now + 5h / + 120d / + 2 min (DEV_CS_SHORT purchasable after release)</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>MS-4095</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-014, COMINGSOON-UI-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_NOPRICE</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y, price null AND cashPrice null</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P8</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-029, COMINGSOON-UI-030, COMINGSOON-UI-031</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_CASHONLY</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y, price null, cashPrice set</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P8</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-033</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_SOON_TAG_PRICE</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Store tag = soon with price set / price null</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P2</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-001, COMINGSOON-UI-002, COMINGSOON-UI-003, COMINGSOON-UI-004, COMINGSOON-UI-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_SOON_TAG_NOPRICE</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Store tag = soon with price set / price null</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P2</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_FLAG_NULL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon empty/null, in stock</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>MS-2314 P3</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>DEV_PREORDER</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Pre-order device; NOSTOCK = stock 0 and pre-order enabled</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>OP24</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>PREORDER-UI-001, PREORDER-UI-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>DEV_PREORDER_NOSTOCK</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Pre-order device; NOSTOCK = stock 0 and pre-order enabled</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>OP24</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>PREORDER-UI-004, PREORDER-UI-005, PREORDER-UI-006, PREORDER-UI-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>DEV_PREORDER_SHORT</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>isPreOrder = Y; releaseDate now + 10d / now + 2 min / quantity &gt; 0</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>MS-4095 P5, Add to cart #34</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>PREORDER-UI-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>DEV_PREORDER_INSTOCK</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>isPreOrder = Y; releaseDate now + 10d / now + 2 min / quantity &gt; 0</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>MS-4095 P5, Add to cart #34</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>PREORDER-UI-008, PREORDER-UI-009, PREORDER-UI-010, PREORDER-UI-011, PREORDER-UI-012, PREORDER-UI-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>DEV_CS_AND_PREORDER</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>TO FILL</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>comingSoon = Y and isPreOrder = Y</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>PREORDER-UI-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Timer setup note</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Env</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>releaseDate values are relative to test start: set them in the test environment right before the run so timer assertions stay deterministic</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>MS-4095</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>COMINGSOON-UI-010, COMINGSOON-UI-011, COMINGSOON-UI-012, COMINGSOON-UI-013, COMINGSOON-UI-014, COMINGSOON-UI-015, COMINGSOON-UI-016, COMINGSOON-UI-017, COMINGSOON-UI-018, COMINGSOON-UI-019, COMINGSOON-UI-020, COMINGSOON-UI-021, COMINGSOON-UI-022, COMINGSOON-UI-024, COMINGSOON-UI-025, COMINGSOON-UI-026, COMINGSOON-UI-027, COMINGSOON-UI-028, COMINGSOON-UI-032</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/test-cases/tcs.xlsx
+++ b/test-cases/tcs.xlsx
@@ -562,9 +562,11 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cash
+DPP: Not selected</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -637,9 +639,11 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cash
+DPP: Selected</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -714,11 +718,11 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User
--with Get onepool Availability For A User, 
-quantity:0</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock 0)
+Purchase option: Cash
+DPP: Selected</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
@@ -782,8 +786,10 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability
--Get onePool Device Availability (Public) --&gt; quantity&gt;0</t>
+          <t>User: Public user
+Category: Wearables
+Device: 6th device in Wearables (OnePool device: local stock 0) - public OnePool stock &gt; 0
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -848,8 +854,10 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability
--Get onePool Device Availability (Public) --&gt; quantity:0</t>
+          <t>User: Public user
+Category: Wearables
+Device: 6th device in Wearables (OnePool device: local stock 0) - public OnePool stock 0
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -910,8 +918,10 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">-"quantity": "1", "isOnePool": "N", in Get Device Availability
-</t>
+          <t>User: Public user
+Category: Wearables
+Device: 6th device in Wearables (fake OnePool: local stock 1, not OnePool)
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
@@ -972,7 +982,10 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 504563459 (OTP login primary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -1050,7 +1063,10 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 0507127863 (OTP login secondary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
@@ -1129,9 +1145,12 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Installment
+Line: voice postpaid number (TO FILL)
+DPP: Not selected</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1220,9 +1239,12 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Installment
+Line: landline postpaid number (TO FILL)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1310,7 +1332,10 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: Public user
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Installment</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
@@ -1384,7 +1409,11 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 504563459 (OTP login primary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Installment
+Line: voice postpaid number (TO FILL)</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1477,7 +1506,10 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 0507127863 (OTP login secondary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Installment</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1559,9 +1591,12 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Free Device
+Line: 504563459 (voice postpaid, active offer)
+DPP: Not selected</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1651,9 +1686,12 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Free Device
+Line: landline postpaid / FWA (TO FILL)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1743,7 +1781,10 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: Public user
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Free Device</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -1817,7 +1858,12 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 504563459 (OTP login primary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Free Device
+Line: landline postpaid (TO FILL)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1910,7 +1956,10 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 0507127863 (OTP login secondary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Free Device</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1996,9 +2045,12 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cashback
+Line: cashback eligible number (TO FILL)
+DPP: Not selected</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2083,9 +2135,12 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cashback
+Line: cashback eligible number (TO FILL)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2170,9 +2225,10 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User</t>
+          <t>User: user with no cashback eligible number (TO FILL)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cashback</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -2243,7 +2299,12 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 504563459 (OTP login primary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cashback
+Line: cashback eligible number (TO FILL)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2332,7 +2393,10 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>-"quantity": "0", "isOnePool": "Y", in Get Device Availability</t>
+          <t>User: 0507127863 (OTP login secondary)
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)
+Purchase option: Cashback</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -2417,9 +2481,9 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Select third device in smart phones, 504563459
--isPreOrder:Y, in get device rules on variations levels , quantity:0
-</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (pre-order variation: stock 0)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2476,10 +2540,10 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Select third device in smart phones, 504563459
--isOnePoolPlus:Y in get device rules
--"quantity": &gt;"0", in Get Device Availability For A User
-</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (fake OnePool: local stock &gt; 0)
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
@@ -2541,10 +2605,10 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Select third device in smart phones, 504563459
--isOnePoolPlus:Y in get device rules
--"quantity": &gt;"0", in Get Device Availability For A User
-</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (fake OnePool: local stock &gt; 0)
+Purchase option: Installment</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
@@ -2607,10 +2671,10 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">-Select third device in smart phones, 504563459
--isOnePoolPlus:Y in get device rules
--"quantity": &gt;"0", in Get Device Availability For A User
-</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (fake OnePool: local stock &gt; 0)
+Purchase option: Free Device</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
@@ -2673,11 +2737,10 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>-Select third device in smart phones, 504563459
--isOnePoolPlus:Y, in get device rules on variations levels
--"quantity": "0", "isOnePool": "Y", in Get Device Availability For A User
--with Get onepool Availability For A User,  quantity:2
--device have partnership email</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: iPhone 16 Plus (OnePool device, OnePool stock 2, partnership device)
+Partnership email: test@stc.com.sa</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
@@ -2845,11 +2908,10 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal smartphone eligible for Add to Cart
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-Purchase option: Cash
-Variation: Available color/storage</t>
+          <t>User: 504563459
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -2912,11 +2974,9 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal Add-to-Cart eligible smartphone supporting installment option
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-DPP: Available
-Variation: Available</t>
+          <t>User: 504563459
+Device: TO FILL (supports Installment and DPP, in stock)
+DPP: Selected</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
@@ -2978,11 +3038,10 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal smartphone supporting installment
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-Eligible postpaid line
-Installment plan available</t>
+          <t>User: 504563459
+Device: TO FILL (supports Installment, in stock)
+Purchase option: Installment
+Line: voice postpaid number (TO FILL)</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -3045,10 +3104,11 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal device supporting Free Device option
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-Eligible postpaid/landline/FWA line with active offer</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: PLUS 6TH
+Purchase option: Free Device
+Line: 504563459</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
@@ -3109,10 +3169,10 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal device supporting Cashback
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-Cashback eligible number available</t>
+          <t>User: 504563459
+Device: TO FILL (supports Cashback, in stock)
+Purchase option: Cashback
+Line: cashback eligible number (TO FILL)</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -3171,10 +3231,8 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Device supporting Cashback
-No cashback eligible numbers
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N</t>
+          <t>User: user with no cashback eligible number (TO FILL)
+Device: TO FILL (supports Cashback)</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -3229,10 +3287,9 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>User: Not logged in
-Device: Normal available device
-Public device availability: quantity &gt; 0
-isOnePool = N</t>
+          <t>User: Public user
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -3292,10 +3349,9 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Primary MSISDN: 504563459
-Device: Normal Add-to-Cart eligible device
-quantity &gt; 0
-isOnePool = N</t>
+          <t>User: 504563459 (OTP login primary)
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
@@ -3353,11 +3409,9 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Secondary MSISDN: 0507127863
-Device: Normal device
-quantity &gt; 0
-isOnePool = N
-Secondary line eligibility must be checked</t>
+          <t>User: 0507127863 (OTP login secondary)
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
@@ -3416,10 +3470,9 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal non-OnePool device
-Get Device Availability For A User: quantity = 0, isOnePool = N
-isOnePoolPlus = N</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: IP16PRO and AWS10 MMax 24M (out of stock)</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -3476,10 +3529,10 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal non-OnePool device
-Get Device Availability For A User: quantity &gt; 0, isOnePool = N
-Available variation</t>
+          <t>User: 504563459
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -3537,11 +3590,9 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Third device in Smart Phones
-isOnePoolPlus = Y in Get Device Rules on variation level
-Get Device Availability For A User: quantity = 0, isOnePool = Y
-Get onePool Availability For A User: quantity &gt; 0</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -3598,10 +3649,9 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: OnePool device
-Get Device Availability For A User: quantity = 0, isOnePool = Y
-Get onePool Availability For A User: quantity = 0</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock 0)</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -3658,10 +3708,9 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Device with isOnePoolPlus = Y in Get Device Rules
-Get Device Availability For A User: quantity &gt; 0
-Device should be processed as normal available inventory</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (fake OnePool: local stock &gt; 0)</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -3720,9 +3769,8 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device variation: quantity = 0
-Get Device Rules: isPreOrder = Y</t>
+          <t>User: 504563459
+Device: TO FILL (pre-order device: stock 0)</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -3779,11 +3827,9 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Add-to-Cart eligible device requiring partnership email
-quantity &gt; 0
-isOnePool = N
-Valid partnership email</t>
+          <t>User: 504563459
+Device: TO FILL (partnership device, in stock)
+Partnership email: test@stc.com.sa</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -3841,11 +3887,11 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Smartphone with at least 2 storage variations
-Storage A: quantity &gt; 0
-Storage B: quantity &gt; 0
-Purchase: Cash</t>
+          <t>User: 504563459
+Device: TO FILL (2 storages in stock)
+Storage A: TO FILL
+Storage B: TO FILL
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
@@ -3903,12 +3949,11 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Smartphone with at least 2 colors
-Color A: quantity &gt; 0
-Color B: quantity &gt; 0
-Same storage
-Purchase: Cash</t>
+          <t>User: 504563459
+Device: TO FILL (2 colors in stock, same storage)
+Color A: TO FILL
+Color B: TO FILL
+Purchase option: Cash</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -3965,11 +4010,9 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Same device
-Variation A: quantity = 0
-Variation B: quantity &gt; 0
-isOnePool = N</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: PLUS 6TH (Variation A out of stock, Variation B in stock)</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
@@ -4027,10 +4070,10 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Normal eligible device
-quantity &gt; 0
-Known color/storage/price</t>
+          <t>User: 504563459
+Cart: empty
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -4086,10 +4129,9 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device A: quantity &gt; 0, isOnePool = N
-Device B: quantity &gt; 0, isOnePool = N
-Both Add-to-Cart eligible</t>
+          <t>User: 504563459
+Device A: WHOOP PEAK BAND 5.0 (Wearables)
+Device B: iPhone 17 Pro Max (Smart phones)</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
@@ -4146,9 +4188,9 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Same normal device + same variation
-quantity sufficient for repeated action</t>
+          <t>User: 504563459
+Cart: 1 x WHOOP PEAK BAND 5.0
+Device: WHOOP PEAK BAND 5.0 (same variation)</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
@@ -4205,8 +4247,8 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-One or more normal devices already in Cart</t>
+          <t>User: 504563459
+Cart: WHOOP PEAK BAND 5.0, iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
@@ -4263,8 +4305,8 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Cart contains one or more Add-to-Cart eligible devices</t>
+          <t>User: 504563459
+Cart: WHOOP PEAK BAND 5.0, iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
@@ -4320,8 +4362,9 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Normal eligible device already added</t>
+          <t>User: 504563459
+Cart: 1 x WHOOP PEAK BAND 5.0
+Categories: Smart phones, Wearables</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -4376,10 +4419,10 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Normal eligible device
-quantity &gt; 0
-Cash</t>
+          <t>User: 504563459
+Cart: empty
+Device: WHOOP PEAK BAND 5.0
+Taps: 5 within 1 second</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
@@ -4436,10 +4479,9 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Normal eligible device
-Availability service: 500 or timeout
-Retry: success with quantity &gt; 0</t>
+          <t>User: 504563459
+Device: WHOOP PEAK BAND 5.0
+Network: OFF then ON</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
@@ -4500,10 +4542,8 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Normal eligible device
-Known product name/color/storage/price
-quantity &gt; 0</t>
+          <t>User: 504563459
+Cart: 1 x WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
@@ -4560,12 +4600,9 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Existing Cart item: Prepaid Order
-New Product: Any Add-to-Cart eligible product
-New Product quantity: &gt; 0
-isOnePool: N
-Purchase option: Cas</t>
+          <t>User: 504563459
+Cart: Prepaid order (TO FILL)
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
@@ -4629,11 +4666,9 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Existing Cart Item: Normal Add-to-Cart eligible device
-Existing Device quantity: &gt; 0
-isOnePool: N
-New Item: Prepaid Order</t>
+          <t>User: 504563459
+Cart: 1 x WHOOP PEAK BAND 5.0
+New item: Prepaid order (TO FILL)</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
@@ -4698,12 +4733,9 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Get User Cart Details: CART ITEM COUNT = X
-Existing Cart Items: X items
-New Product: Add-to-Cart eligible product
-New Product quantity: &gt; 0
-isOnePool: N</t>
+          <t>User: 504563459
+Cart: maximum allowed items (CART ITEM COUNT = X)
+Device: iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
@@ -4768,10 +4800,8 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Product: Back Order device
-Device Rule API: RESERVABLE = "Y"
-Product Status: Back Order
+          <t>User: 504563459
+Device: TO FILL (back order, reservable)
 Action: Reserve Now</t>
         </is>
       </c>
@@ -4838,11 +4868,9 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: OnePool eligible device
-Get Device Availability For A User: isOnePool = "Y"
-Local quantity: 0
-OnePool Availability: quantity &gt; 0</t>
+          <t>User: 504563459
+Category: Smart phones
+Device: 3rd device in Smart phones (OnePool device: local stock 0, OnePool stock &gt; 0)</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -4907,10 +4935,8 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Pre Order eligible device
-Device Rule API: isPreOrder = "Y"
-Product Type: Pre Order</t>
+          <t>User: 504563459
+Device: TO FILL (pre-order device)</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -4974,12 +5000,10 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Existing Cart Item: Pre Order device
-Device Rule: isPreOrder = "Y"
-New Product: Normal available device
-New Device quantity: &gt; 0
-isOnePool: N</t>
+          <t>User: 504563459
+Cart: pre-order device (TO FILL)
+Category: Wearables
+Device: WHOOP PEAK BAND 5.0</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
@@ -5043,10 +5067,9 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Existing Cart Item: Normal device, quantity &gt; 0
-New Product: Pre Order device
-New Product Device Rule: isPreOrder = "Y"</t>
+          <t>User: 504563459
+Cart: 1 x WHOOP PEAK BAND 5.0
+Device: TO FILL (pre-order device)</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -5109,12 +5132,9 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Normal Add-to-Cart eligible device
-quantity: &gt; 0
-isOnePool: N
-STC Protect: Eligible/Available
-Selection: Add STC Protect</t>
+          <t>User: 504563459
+Device: TO FILL (STC Protect eligible, in stock)
+STC Protect: Selected</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
@@ -5179,12 +5199,9 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Same STC Protect eligible device
-quantity: &gt; 0
-isOnePool: N
-STC Protect: Available
-Selection: Continue without STC Protec</t>
+          <t>User: 504563459
+Device: TO FILL (STC Protect eligible, in stock)
+STC Protect: Not selected</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
@@ -5249,12 +5266,9 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Device: Add-to-Cart eligible Partnership device
-quantity: &gt; 0
-isOnePool: N
-Partnership: Enabled
-Email: Valid partnership email "test@stc.com.sa"</t>
+          <t>User: 504563459
+Device: TO FILL (partnership device, in stock)
+Partnership email: test@stc.com.sa</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -5318,10 +5332,8 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>MSISDN: 504563459
-Product: Back Order device
-Device Rule API: RESERVABLE = "N"
-Product Status: Back Order</t>
+          <t>User: 504563459
+Device: TO FILL (back order, not reservable)</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -5386,6 +5398,7 @@
       <c r="H42" s="11" t="inlineStr">
         <is>
           <t>User: 504563459
+Category: Smart phones
 Device: PLUS 6TH (Variation A out of stock, Variation B in stock)</t>
         </is>
       </c>
@@ -5451,7 +5464,9 @@
       <c r="H43" s="11" t="inlineStr">
         <is>
           <t>User: 504563459
+Category: Smart phones
 Device: PLUS 6TH
+Purchase option: Free Device
 Line: 504563459</t>
         </is>
       </c>
